--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13103,22 +13103,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13524,17 +13524,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,14 +12904,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12761,12 +12761,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,29 +13448,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -12751,22 +12751,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12953,12 +12953,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13081,12 +13081,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,29 +13448,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -13081,12 +13081,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,29 +13448,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12847,22 +12847,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -12975,22 +12975,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13071,22 +13071,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13487,22 +13487,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12623,7 +12623,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12719,22 +12719,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12975,22 +12975,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12687,22 +12687,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,14 +12968,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12655,22 +12655,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
